--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Digest.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Digest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="196">
   <si>
     <t>Property</t>
   </si>
@@ -489,6 +489,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Binary.meta.tag</t>
   </si>
   <si>
@@ -594,6 +601,13 @@
   </si>
   <si>
     <t>Very often, a server will also know of a resource that references the binary, and can automatically apply the appropriate access rules based on that reference. However, there are some circumstances where this is not appropriate, e.g. the binary is uploaded directly to the server without any linking resource, the binary is referred to from multiple different resources, and/or the binary is content such as an application logo that has less protection than any of the resources that reference it.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Binary.data</t>
@@ -967,7 +981,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="60.26953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2227,21 +2241,21 @@
         <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>74</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2267,13 +2281,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2299,13 +2313,13 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2323,7 +2337,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2332,21 +2346,21 @@
         <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>74</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2372,13 +2386,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2428,7 +2442,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2448,10 +2462,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2474,16 +2488,16 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2509,13 +2523,13 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2533,7 +2547,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2553,10 +2567,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2579,13 +2593,13 @@
         <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2594,7 +2608,7 @@
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>74</v>
@@ -2612,13 +2626,13 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2636,7 +2650,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -2651,15 +2665,15 @@
         <v>95</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2682,16 +2696,16 @@
         <v>84</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2741,7 +2755,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2750,21 +2764,21 @@
         <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>101</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2787,16 +2801,16 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2846,7 +2860,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2861,7 +2875,7 @@
         <v>95</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Digest.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Digest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="192">
   <si>
     <t>Property</t>
   </si>
@@ -489,13 +489,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Binary.meta.tag</t>
   </si>
   <si>
@@ -601,13 +594,6 @@
   </si>
   <si>
     <t>Very often, a server will also know of a resource that references the binary, and can automatically apply the appropriate access rules based on that reference. However, there are some circumstances where this is not appropriate, e.g. the binary is uploaded directly to the server without any linking resource, the binary is referred to from multiple different resources, and/or the binary is content such as an application logo that has less protection than any of the resources that reference it.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Binary.data</t>
@@ -981,7 +967,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="60.26953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2241,21 +2227,21 @@
         <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2281,13 +2267,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2313,31 +2299,31 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2346,21 +2332,21 @@
         <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>152</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2386,13 +2372,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2442,7 +2428,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2462,10 +2448,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2488,16 +2474,16 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2523,31 +2509,31 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2567,10 +2553,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2593,13 +2579,13 @@
         <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2608,32 +2594,32 @@
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="S16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
       </c>
@@ -2650,7 +2636,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -2665,15 +2651,15 @@
         <v>95</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2696,16 +2682,16 @@
         <v>84</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2755,7 +2741,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2764,21 +2750,21 @@
         <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2801,16 +2787,16 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2860,7 +2846,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2875,7 +2861,7 @@
         <v>95</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
